--- a/data/trans_dic/P1421-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P1421-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,12</t>
+          <t>1,82; 5,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 5,25</t>
+          <t>1,8; 5,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,39</t>
+          <t>3,3; 7,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 10,06</t>
+          <t>4,41; 10,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 10,28</t>
+          <t>4,61; 10,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,37</t>
+          <t>1,99; 6,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,26; 11,97</t>
+          <t>7,26; 12,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 6,32</t>
+          <t>3,13; 6,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,99</t>
+          <t>2,25; 5,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,81</t>
+          <t>2,19; 4,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>5,77; 8,75</t>
+          <t>5,8; 8,86</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 4,35</t>
+          <t>1,06; 4,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,45</t>
+          <t>0,27; 2,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,34</t>
+          <t>0,25; 2,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,43</t>
+          <t>1,91; 5,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,05</t>
+          <t>5,5; 11,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,56</t>
+          <t>2,6; 7,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,98</t>
+          <t>3,13; 8,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,5; 13,64</t>
+          <t>8,62; 13,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,06</t>
+          <t>3,78; 6,98</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,17</t>
+          <t>1,55; 4,2</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,56</t>
+          <t>1,81; 4,51</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,5</t>
+          <t>5,4; 8,41</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>7,43%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,34</t>
+          <t>1,57; 4,35</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,47</t>
+          <t>0,74; 2,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,0</t>
+          <t>0,22; 1,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,91</t>
+          <t>2,88; 7,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,74; 12,27</t>
+          <t>3,75; 11,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 9,38</t>
+          <t>3,38; 9,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 12,49</t>
+          <t>3,96; 12,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,16; 18,18</t>
+          <t>10,46; 18,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,48</t>
+          <t>2,57; 5,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,99</t>
+          <t>1,72; 3,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,79</t>
+          <t>1,43; 3,85</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 8,13</t>
+          <t>5,61; 9,51</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,31</t>
+          <t>1,56; 3,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,22</t>
+          <t>0,83; 2,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,71</t>
+          <t>0,45; 1,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,38</t>
+          <t>3,35; 5,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,42</t>
+          <t>4,53; 8,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,62; 6,81</t>
+          <t>3,73; 7,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 6,86</t>
+          <t>3,73; 6,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,03; 12,67</t>
+          <t>10,34; 14,32</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,81</t>
+          <t>2,93; 4,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,77</t>
+          <t>2,14; 3,68</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,41</t>
+          <t>1,99; 3,49</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,38</t>
+          <t>6,75; 9,06</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,9%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,94</t>
+          <t>1,19; 4,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,25</t>
+          <t>0,42; 2,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,76</t>
+          <t>1,41; 4,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 7,99</t>
+          <t>3,2; 7,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,71</t>
+          <t>3,91; 7,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,94; 8,71</t>
+          <t>4,76; 8,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,38; 9,52</t>
+          <t>5,48; 9,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,43; 15,04</t>
+          <t>11,53; 15,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 5,99</t>
+          <t>3,07; 5,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,54</t>
+          <t>3,3; 5,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,75; 6,22</t>
+          <t>3,87; 6,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,79; 11,63</t>
+          <t>8,61; 11,32</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,77</t>
+          <t>0,29; 2,63</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,59</t>
+          <t>0,36; 3,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,1; 7,52</t>
+          <t>1,04; 7,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,45; 5,78</t>
+          <t>3,52; 5,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,13; 5,57</t>
+          <t>3,06; 5,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,79; 6,44</t>
+          <t>3,65; 6,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,15; 11,09</t>
+          <t>6,99; 10,75</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 4,88</t>
+          <t>2,92; 4,89</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,84</t>
+          <t>2,68; 4,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,17</t>
+          <t>3,04; 5,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,02; 9,48</t>
+          <t>5,98; 9,07</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 3,01</t>
+          <t>1,9; 3,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 1,65</t>
+          <t>0,88; 1,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 1,89</t>
+          <t>1,07; 1,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,33; 5,04</t>
+          <t>3,76; 5,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,63</t>
+          <t>4,91; 6,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,58; 6,09</t>
+          <t>4,62; 6,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,75; 6,35</t>
+          <t>4,77; 6,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,48; 11,5</t>
+          <t>10,26; 12,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,69; 4,59</t>
+          <t>3,66; 4,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,92; 3,81</t>
+          <t>2,88; 3,73</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 3,97</t>
+          <t>3,02; 3,91</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,44; 8,21</t>
+          <t>7,21; 8,49</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26423</t>
+          <t>27627</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>42509</t>
+          <t>46198</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68931</t>
+          <t>73825</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9449; 24261</t>
+          <t>8629; 24429</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 10785</t>
+          <t>0; 12704</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7126; 22520</t>
+          <t>7706; 21505</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17824; 37334</t>
+          <t>18170; 38790</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12995; 30857</t>
+          <t>13509; 33097</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14414; 32336</t>
+          <t>14482; 33173</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6617; 22103</t>
+          <t>6896; 21363</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32502; 53541</t>
+          <t>35479; 59321</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>24761; 49290</t>
+          <t>24390; 47719</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16630; 37492</t>
+          <t>16933; 37688</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17062; 37345</t>
+          <t>16967; 38185</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54994; 83339</t>
+          <t>60307; 92024</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15297</t>
+          <t>16001</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41288</t>
+          <t>45526</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>56585</t>
+          <t>61527</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3851; 15955</t>
+          <t>3897; 15288</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1032; 10281</t>
+          <t>1143; 10846</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>923; 8835</t>
+          <t>938; 8058</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8746; 24564</t>
+          <t>9220; 25452</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20257; 41109</t>
+          <t>20449; 41121</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8980; 25553</t>
+          <t>8802; 25382</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11853; 29707</t>
+          <t>11667; 30730</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32461; 52077</t>
+          <t>36418; 57723</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28053; 52164</t>
+          <t>27944; 51553</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12635; 31549</t>
+          <t>11717; 31802</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14515; 34211</t>
+          <t>13530; 33812</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>44965; 70885</t>
+          <t>48883; 76142</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20420</t>
+          <t>22145</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23324</t>
+          <t>26792</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43744</t>
+          <t>48937</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8404; 23542</t>
+          <t>8492; 23611</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3943; 15515</t>
+          <t>4636; 16257</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1153; 10424</t>
+          <t>1136; 10355</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5698; 39466</t>
+          <t>13575; 35166</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6279; 20595</t>
+          <t>6296; 19861</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7942; 24401</t>
+          <t>8781; 24119</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6410; 20747</t>
+          <t>6586; 21478</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16962; 30346</t>
+          <t>19607; 35337</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17777; 38888</t>
+          <t>18237; 39035</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15189; 35469</t>
+          <t>15266; 34454</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9568; 26046</t>
+          <t>9814; 26514</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17230; 67804</t>
+          <t>36954; 62601</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49064</t>
+          <t>51328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>92081</t>
+          <t>103887</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>141144</t>
+          <t>155215</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19658; 40941</t>
+          <t>19310; 40568</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9689; 25714</t>
+          <t>9608; 25323</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4723; 19636</t>
+          <t>5155; 19305</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>36184; 66034</t>
+          <t>37880; 66686</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>32769; 60165</t>
+          <t>32325; 57442</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>27651; 52083</t>
+          <t>28561; 55528</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>30873; 56652</t>
+          <t>30833; 56231</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49211; 123923</t>
+          <t>89012; 123287</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57001; 93963</t>
+          <t>57261; 91382</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>40462; 72454</t>
+          <t>41148; 70708</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38675; 67395</t>
+          <t>39372; 68878</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>98794; 168732</t>
+          <t>134584; 180635</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25778</t>
+          <t>27707</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>102614</t>
+          <t>110227</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>128393</t>
+          <t>137934</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4331; 17302</t>
+          <t>4162; 17137</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1969; 11470</t>
+          <t>2128; 12542</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8636; 23353</t>
+          <t>8761; 24921</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16422; 37841</t>
+          <t>18112; 41598</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20811; 43838</t>
+          <t>22266; 44027</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37593; 66208</t>
+          <t>36217; 64384</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39744; 70291</t>
+          <t>40473; 69854</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>78980; 125990</t>
+          <t>95562; 126706</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>28527; 55078</t>
+          <t>28210; 54947</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41885; 70386</t>
+          <t>41974; 70104</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>50993; 84557</t>
+          <t>52587; 88487</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>102100; 152525</t>
+          <t>120032; 157803</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6973</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>68696</t>
+          <t>73398</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>75669</t>
+          <t>80529</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>852; 8247</t>
+          <t>850; 7853</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>958; 9590</t>
+          <t>955; 9208</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 7190</t>
+          <t>0; 6490</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2639; 18080</t>
+          <t>2461; 17206</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43101; 72157</t>
+          <t>43958; 72723</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34721; 61830</t>
+          <t>33923; 63837</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40986; 69683</t>
+          <t>39453; 68878</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>54289; 84202</t>
+          <t>58867; 90512</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>46109; 75428</t>
+          <t>45165; 75645</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37467; 66637</t>
+          <t>36826; 64240</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40764; 70826</t>
+          <t>41561; 71768</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>60225; 94820</t>
+          <t>64555; 97855</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>143955</t>
+          <t>151938</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>370512</t>
+          <t>406028</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>514467</t>
+          <t>557966</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>62000; 98579</t>
+          <t>62055; 99086</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>29492; 56498</t>
+          <t>30079; 57090</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35466; 64004</t>
+          <t>36084; 63129</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>112325; 170114</t>
+          <t>129423; 180374</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>169732; 223849</t>
+          <t>165951; 222963</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>162622; 216076</t>
+          <t>163897; 218186</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>167639; 224112</t>
+          <t>168587; 225056</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>302748; 410584</t>
+          <t>372584; 441661</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>245020; 304844</t>
+          <t>243098; 304858</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>203746; 265577</t>
+          <t>200729; 260164</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>211955; 274572</t>
+          <t>208646; 270738</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>447284; 570279</t>
+          <t>509402; 599968</t>
         </is>
       </c>
     </row>
